--- a/GEC_ERP/Vendor_Master_Generated.xlsx
+++ b/GEC_ERP/Vendor_Master_Generated.xlsx
@@ -475,7 +475,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
